--- a/PUM.DE.xlsx
+++ b/PUM.DE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8323A2FA-6EE3-4458-8BC1-B56197884B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF26DAD-30CF-443E-9221-177DF5A52A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{DF056538-1695-47DF-BC32-BA7DD1F9A83B}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{DF056538-1695-47DF-BC32-BA7DD1F9A83B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,24 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={CF0A33D2-AD11-4BDD-A1E8-78D7360A19D7}</author>
+  </authors>
+  <commentList>
+    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{CF0A33D2-AD11-4BDD-A1E8-78D7360A19D7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Adjusted numbers</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -230,13 +248,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -291,6 +315,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -311,31 +341,35 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -353,6 +387,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Oscar Settje" id="{341856C5-C3D4-43DE-A51A-08F910ECF662}" userId="7ff36870b9739543" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -670,6 +710,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="L2" dT="2026-08-18T15:15:19.67" personId="{341856C5-C3D4-43DE-A51A-08F910ECF662}" id="{CF0A33D2-AD11-4BDD-A1E8-78D7360A19D7}">
+    <text>Adjusted numbers</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46746356-DDAA-46AE-8571-B699D0C98654}">
   <dimension ref="A1:J10"/>
@@ -692,7 +740,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="2">
-        <v>25.98</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -700,10 +748,10 @@
         <v>3</v>
       </c>
       <c r="I3" s="4">
-        <v>147.22999999999999</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>57</v>
+        <v>147.20890499999999</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -715,7 +763,7 @@
       </c>
       <c r="I4" s="4">
         <f>+I2*I3</f>
-        <v>3825.0353999999998</v>
+        <v>3797.9897489999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -728,8 +776,8 @@
       <c r="I5" s="4">
         <v>326.2</v>
       </c>
-      <c r="J5" s="14" t="s">
-        <v>57</v>
+      <c r="J5" s="15" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -740,8 +788,8 @@
         <f>1139.8+544</f>
         <v>1683.8</v>
       </c>
-      <c r="J6" s="14" t="s">
-        <v>57</v>
+      <c r="J6" s="15" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -750,7 +798,7 @@
       </c>
       <c r="I7" s="4">
         <f>+I4-I5+I6</f>
-        <v>5182.6354000000001</v>
+        <v>5155.5897489999998</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -773,7 +821,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{358FBAD2-1CB2-460A-BF2B-D7C2BA58E00E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{358FBAD2-1CB2-460A-BF2B-D7C2BA58E00E}">
   <dimension ref="A1:BL264"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -896,7 +944,9 @@
       <c r="O3" s="12">
         <v>774.5</v>
       </c>
-      <c r="P3" s="12"/>
+      <c r="P3" s="12">
+        <v>674.1</v>
+      </c>
       <c r="Q3" s="12"/>
       <c r="R3" s="12"/>
       <c r="S3" s="12"/>
@@ -979,19 +1029,21 @@
         <v>753.7</v>
       </c>
       <c r="L4" s="12">
-        <v>779.9</v>
+        <v>709</v>
       </c>
       <c r="M4" s="12">
         <v>678.1</v>
       </c>
       <c r="N4" s="12">
         <f t="shared" ref="N4:N21" si="0">+Z4-SUM(K4:M4)</f>
-        <v>276.90000000000055</v>
+        <v>347.80000000000018</v>
       </c>
       <c r="O4" s="12">
         <v>655.6</v>
       </c>
-      <c r="P4" s="12"/>
+      <c r="P4" s="12">
+        <v>600.4</v>
+      </c>
       <c r="Q4" s="12"/>
       <c r="R4" s="12"/>
       <c r="S4" s="12"/>
@@ -1086,7 +1138,9 @@
       <c r="O5" s="12">
         <v>433.8</v>
       </c>
-      <c r="P5" s="12"/>
+      <c r="P5" s="12">
+        <v>416</v>
+      </c>
       <c r="Q5" s="12"/>
       <c r="R5" s="12"/>
       <c r="S5" s="12"/>
@@ -1181,7 +1235,9 @@
       <c r="O6" s="12">
         <v>1089.5999999999999</v>
       </c>
-      <c r="P6" s="12"/>
+      <c r="P6" s="12">
+        <v>935.6</v>
+      </c>
       <c r="Q6" s="12"/>
       <c r="R6" s="12"/>
       <c r="S6" s="12"/>
@@ -1263,19 +1319,21 @@
         <v>594.29999999999995</v>
       </c>
       <c r="L7" s="12">
-        <v>597.79999999999995</v>
+        <v>579.20000000000005</v>
       </c>
       <c r="M7" s="12">
         <v>635.5</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>500.90000000000009</v>
+        <v>519.5</v>
       </c>
       <c r="O7" s="12">
         <v>546.29999999999995</v>
       </c>
-      <c r="P7" s="12"/>
+      <c r="P7" s="12">
+        <v>552.1</v>
+      </c>
       <c r="Q7" s="12"/>
       <c r="R7" s="12"/>
       <c r="S7" s="12"/>
@@ -1357,19 +1415,21 @@
         <v>295.7</v>
       </c>
       <c r="L8" s="12">
-        <v>283.39999999999998</v>
+        <v>230.9</v>
       </c>
       <c r="M8" s="12">
         <v>274.39999999999998</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" si="0"/>
-        <v>0.40000000000009095</v>
+        <v>52.899999999999977</v>
       </c>
       <c r="O8" s="12">
         <v>227.9</v>
       </c>
-      <c r="P8" s="12"/>
+      <c r="P8" s="12">
+        <v>202.8</v>
+      </c>
       <c r="Q8" s="12"/>
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
@@ -1451,19 +1511,21 @@
         <v>1529.5</v>
       </c>
       <c r="L9" s="12">
-        <v>1341.2</v>
+        <v>1270.2</v>
       </c>
       <c r="M9" s="12">
         <v>1385.7</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="0"/>
-        <v>678.60000000000036</v>
+        <v>749.60000000000036</v>
       </c>
       <c r="O9" s="12">
         <v>1335.7</v>
       </c>
-      <c r="P9" s="12"/>
+      <c r="P9" s="12">
+        <v>1094.8</v>
+      </c>
       <c r="Q9" s="12"/>
       <c r="R9" s="12"/>
       <c r="S9" s="12"/>
@@ -1557,7 +1619,9 @@
       <c r="O10" s="12">
         <v>528.1</v>
       </c>
-      <c r="P10" s="12"/>
+      <c r="P10" s="12">
+        <v>595.79999999999995</v>
+      </c>
       <c r="Q10" s="12"/>
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
@@ -1641,19 +1705,21 @@
         <v>2076</v>
       </c>
       <c r="L11" s="13">
-        <v>1942.2</v>
+        <v>1871.3</v>
       </c>
       <c r="M11" s="13">
         <v>1955.7</v>
       </c>
       <c r="N11" s="13">
         <f t="shared" si="0"/>
-        <v>1322.3000000000002</v>
+        <v>1393.1999999999998</v>
       </c>
       <c r="O11" s="13">
         <v>1863.8</v>
       </c>
-      <c r="P11" s="13"/>
+      <c r="P11" s="13">
+        <v>1690.6</v>
+      </c>
       <c r="Q11" s="13"/>
       <c r="R11" s="13"/>
       <c r="S11" s="12"/>
@@ -1737,19 +1803,21 @@
         <v>1100.9000000000001</v>
       </c>
       <c r="L12" s="12">
-        <v>1047.5999999999999</v>
+        <v>1006.9</v>
       </c>
       <c r="M12" s="12">
         <v>1070.8</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="0"/>
-        <v>797.19999999999982</v>
+        <v>837.89999999999964</v>
       </c>
       <c r="O12" s="12">
         <v>974.9</v>
       </c>
-      <c r="P12" s="12"/>
+      <c r="P12" s="12">
+        <v>878.3</v>
+      </c>
       <c r="Q12" s="12"/>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
@@ -1838,7 +1906,7 @@
         <v>1105.4999999999998</v>
       </c>
       <c r="J13" s="12">
-        <f t="shared" ref="J13:O13" si="2">+J11-J12</f>
+        <f t="shared" ref="J13:P13" si="2">+J11-J12</f>
         <v>1082.9000000000001</v>
       </c>
       <c r="K13" s="12">
@@ -1847,7 +1915,7 @@
       </c>
       <c r="L13" s="12">
         <f t="shared" si="2"/>
-        <v>894.60000000000014</v>
+        <v>864.4</v>
       </c>
       <c r="M13" s="12">
         <f t="shared" si="2"/>
@@ -1855,13 +1923,16 @@
       </c>
       <c r="N13" s="12">
         <f t="shared" si="2"/>
-        <v>525.10000000000036</v>
+        <v>555.30000000000018</v>
       </c>
       <c r="O13" s="12">
         <f t="shared" si="2"/>
         <v>888.9</v>
       </c>
-      <c r="P13" s="12"/>
+      <c r="P13" s="12">
+        <f t="shared" si="2"/>
+        <v>812.3</v>
+      </c>
       <c r="Q13" s="12"/>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
@@ -1960,19 +2031,21 @@
         <v>5.5</v>
       </c>
       <c r="L14" s="12">
-        <v>6.9</v>
+        <v>20.2</v>
       </c>
       <c r="M14" s="12">
         <v>5.2</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="0"/>
-        <v>74.800000000000011</v>
+        <v>61.500000000000007</v>
       </c>
       <c r="O14" s="12">
         <v>23.9</v>
       </c>
-      <c r="P14" s="12"/>
+      <c r="P14" s="12">
+        <v>18.399999999999999</v>
+      </c>
       <c r="Q14" s="12"/>
       <c r="R14" s="12"/>
       <c r="S14" s="12"/>
@@ -2057,7 +2130,8 @@
         <v>922.9</v>
       </c>
       <c r="L15" s="12">
-        <v>914.7</v>
+        <f>909+84.6</f>
+        <v>993.6</v>
       </c>
       <c r="M15" s="12">
         <f>850.6+10.1</f>
@@ -2065,13 +2139,16 @@
       </c>
       <c r="N15" s="12">
         <f t="shared" si="0"/>
-        <v>1030.9999999999995</v>
+        <v>952.09999999999991</v>
       </c>
       <c r="O15" s="12">
         <f>848.5+12.6</f>
         <v>861.1</v>
       </c>
-      <c r="P15" s="12"/>
+      <c r="P15" s="12">
+        <f>872.6+11.2</f>
+        <v>883.80000000000007</v>
+      </c>
       <c r="Q15" s="12"/>
       <c r="R15" s="12"/>
       <c r="S15" s="12"/>
@@ -2161,7 +2238,7 @@
         <v>236.99999999999989</v>
       </c>
       <c r="J16" s="12">
-        <f t="shared" ref="J16:O16" si="5">+J13+J14-J15</f>
+        <f t="shared" ref="J16:P16" si="5">+J13+J14-J15</f>
         <v>108.90000000000009</v>
       </c>
       <c r="K16" s="12">
@@ -2170,7 +2247,7 @@
       </c>
       <c r="L16" s="12">
         <f t="shared" si="5"/>
-        <v>-13.199999999999932</v>
+        <v>-109</v>
       </c>
       <c r="M16" s="12">
         <f t="shared" si="5"/>
@@ -2178,13 +2255,16 @@
       </c>
       <c r="N16" s="12">
         <f t="shared" si="5"/>
-        <v>-431.09999999999923</v>
+        <v>-335.29999999999973</v>
       </c>
       <c r="O16" s="12">
         <f t="shared" si="5"/>
         <v>51.699999999999932</v>
       </c>
-      <c r="P16" s="12"/>
+      <c r="P16" s="12">
+        <f t="shared" si="5"/>
+        <v>-53.100000000000136</v>
+      </c>
       <c r="Q16" s="12"/>
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
@@ -2283,20 +2363,21 @@
         <v>42</v>
       </c>
       <c r="L17" s="12">
-        <f>84.6+46.6</f>
-        <v>131.19999999999999</v>
+        <v>43.7</v>
       </c>
       <c r="M17" s="12">
         <v>43.8</v>
       </c>
       <c r="N17" s="12">
         <f t="shared" si="0"/>
-        <v>-51.300000000000011</v>
+        <v>36.199999999999989</v>
       </c>
       <c r="O17" s="12">
         <v>15.6</v>
       </c>
-      <c r="P17" s="12"/>
+      <c r="P17" s="12">
+        <v>20.3</v>
+      </c>
       <c r="Q17" s="12"/>
       <c r="R17" s="12"/>
       <c r="S17" s="12"/>
@@ -2369,7 +2450,7 @@
         <v>190.79999999999973</v>
       </c>
       <c r="F18" s="12">
-        <f t="shared" ref="F18:O18" si="8">+F16-F17</f>
+        <f t="shared" ref="F18:P18" si="8">+F16-F17</f>
         <v>27.300000000000097</v>
       </c>
       <c r="G18" s="12">
@@ -2394,7 +2475,7 @@
       </c>
       <c r="L18" s="12">
         <f t="shared" si="8"/>
-        <v>-144.39999999999992</v>
+        <v>-152.69999999999999</v>
       </c>
       <c r="M18" s="12">
         <f t="shared" si="8"/>
@@ -2402,13 +2483,16 @@
       </c>
       <c r="N18" s="12">
         <f t="shared" si="8"/>
-        <v>-379.79999999999922</v>
+        <v>-371.49999999999972</v>
       </c>
       <c r="O18" s="12">
         <f t="shared" si="8"/>
         <v>36.09999999999993</v>
       </c>
-      <c r="P18" s="12"/>
+      <c r="P18" s="12">
+        <f t="shared" si="8"/>
+        <v>-73.400000000000134</v>
+      </c>
       <c r="Q18" s="12"/>
       <c r="R18" s="12"/>
       <c r="S18" s="12"/>
@@ -2507,19 +2591,21 @@
         <v>4.2</v>
       </c>
       <c r="L19" s="12">
-        <v>94.7</v>
+        <v>94.3</v>
       </c>
       <c r="M19" s="12">
         <v>37.9</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="0"/>
-        <v>-16.100000000000009</v>
+        <v>-15.700000000000003</v>
       </c>
       <c r="O19" s="12">
         <v>9.8000000000000007</v>
       </c>
-      <c r="P19" s="12"/>
+      <c r="P19" s="12">
+        <v>-0.6</v>
+      </c>
       <c r="Q19" s="12"/>
       <c r="R19" s="12"/>
       <c r="S19" s="12"/>
@@ -2592,7 +2678,7 @@
         <v>142.89999999999972</v>
       </c>
       <c r="F20" s="12">
-        <f t="shared" ref="F20:O20" si="11">+F18-F19</f>
+        <f t="shared" ref="F20:P20" si="11">+F18-F19</f>
         <v>22.400000000000098</v>
       </c>
       <c r="G20" s="12">
@@ -2617,7 +2703,7 @@
       </c>
       <c r="L20" s="12">
         <f t="shared" si="11"/>
-        <v>-239.09999999999991</v>
+        <v>-247</v>
       </c>
       <c r="M20" s="12">
         <f t="shared" si="11"/>
@@ -2625,13 +2711,16 @@
       </c>
       <c r="N20" s="12">
         <f t="shared" si="11"/>
-        <v>-363.69999999999919</v>
+        <v>-355.79999999999973</v>
       </c>
       <c r="O20" s="12">
         <f t="shared" si="11"/>
         <v>26.29999999999993</v>
       </c>
-      <c r="P20" s="12"/>
+      <c r="P20" s="12">
+        <f t="shared" si="11"/>
+        <v>-72.800000000000139</v>
+      </c>
       <c r="Q20" s="12"/>
       <c r="R20" s="12"/>
       <c r="S20" s="12"/>
@@ -2730,19 +2819,21 @@
         <v>11.1</v>
       </c>
       <c r="L21" s="12">
-        <v>7.9</v>
+        <v>0.1</v>
       </c>
       <c r="M21" s="12">
         <v>10</v>
       </c>
       <c r="N21" s="12">
         <f t="shared" si="0"/>
-        <v>-27.099999999999998</v>
+        <v>-19.299999999999997</v>
       </c>
       <c r="O21" s="12">
         <v>0</v>
       </c>
-      <c r="P21" s="12"/>
+      <c r="P21" s="16">
+        <v>0</v>
+      </c>
       <c r="Q21" s="12"/>
       <c r="R21" s="12"/>
       <c r="S21" s="12"/>
@@ -2816,7 +2907,7 @@
         <v>131.59999999999971</v>
       </c>
       <c r="F22" s="12">
-        <f t="shared" ref="F22:O22" si="14">+F20-F21</f>
+        <f t="shared" ref="F22:P22" si="14">+F20-F21</f>
         <v>0.80000000000009663</v>
       </c>
       <c r="G22" s="12">
@@ -2841,7 +2932,7 @@
       </c>
       <c r="L22" s="12">
         <f t="shared" si="14"/>
-        <v>-246.99999999999991</v>
+        <v>-247.1</v>
       </c>
       <c r="M22" s="12">
         <f t="shared" si="14"/>
@@ -2849,13 +2940,16 @@
       </c>
       <c r="N22" s="12">
         <f t="shared" si="14"/>
-        <v>-336.59999999999917</v>
+        <v>-336.49999999999972</v>
       </c>
       <c r="O22" s="12">
         <f t="shared" si="14"/>
         <v>26.29999999999993</v>
       </c>
-      <c r="P22" s="12"/>
+      <c r="P22" s="12">
+        <f t="shared" si="14"/>
+        <v>-72.800000000000139</v>
+      </c>
       <c r="Q22" s="12"/>
       <c r="R22" s="12"/>
       <c r="S22" s="12"/>
@@ -3007,7 +3101,7 @@
         <v>0.87838739821118483</v>
       </c>
       <c r="F24" s="7">
-        <f t="shared" ref="F24:O24" si="17">+F22/F25</f>
+        <f t="shared" ref="F24:P24" si="17">+F22/F25</f>
         <v>5.3386720053393167E-3</v>
       </c>
       <c r="G24" s="7">
@@ -3032,7 +3126,7 @@
       </c>
       <c r="L24" s="7">
         <f t="shared" si="17"/>
-        <v>-1.6732199307509137</v>
+        <v>-1.6738973477269268</v>
       </c>
       <c r="M24" s="7">
         <f t="shared" si="17"/>
@@ -3040,13 +3134,16 @@
       </c>
       <c r="N24" s="7">
         <f t="shared" si="17"/>
-        <v>-2.2824981352139364</v>
+        <v>-2.2818200311927832</v>
       </c>
       <c r="O24" s="7">
         <f t="shared" si="17"/>
         <v>0.17863207226787972</v>
       </c>
-      <c r="P24" s="7"/>
+      <c r="P24" s="7">
+        <f t="shared" si="17"/>
+        <v>-0.49453530002142293</v>
+      </c>
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
       <c r="S24" s="4"/>
@@ -3156,7 +3253,9 @@
       <c r="O25" s="4">
         <v>147.22999999999999</v>
       </c>
-      <c r="P25" s="4"/>
+      <c r="P25" s="4">
+        <v>147.20890499999999</v>
+      </c>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
@@ -3295,12 +3394,12 @@
         <v>0.15497931591161329</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" ref="K27:O27" si="20">+K11/G11-1</f>
+        <f t="shared" ref="K27:P27" si="20">+K11/G11-1</f>
         <v>-1.2510107976977713E-2</v>
       </c>
       <c r="L27" s="8">
         <f t="shared" si="20"/>
-        <v>-8.2699664667264972E-2</v>
+        <v>-0.11618570821329066</v>
       </c>
       <c r="M27" s="8">
         <f t="shared" si="20"/>
@@ -3308,13 +3407,16 @@
       </c>
       <c r="N27" s="8">
         <f t="shared" si="20"/>
-        <v>-0.42242508954311164</v>
+        <v>-0.39145627675373473</v>
       </c>
       <c r="O27" s="8">
         <f t="shared" si="20"/>
         <v>-0.10221579961464355</v>
       </c>
-      <c r="P27" s="8"/>
+      <c r="P27" s="8">
+        <f t="shared" si="20"/>
+        <v>-9.656388606850852E-2</v>
+      </c>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
       <c r="S27" s="6"/>
@@ -3406,7 +3508,7 @@
       </c>
       <c r="L28" s="9">
         <f t="shared" ref="L28:M28" si="23">+L13/L11</f>
-        <v>0.46061167747914744</v>
+        <v>0.46192486506706565</v>
       </c>
       <c r="M28" s="9">
         <f t="shared" si="23"/>
@@ -3414,13 +3516,16 @@
       </c>
       <c r="N28" s="9">
         <f t="shared" ref="N28:O28" si="24">+N13/N11</f>
-        <v>0.39711109430537722</v>
+        <v>0.39857881136950923</v>
       </c>
       <c r="O28" s="9">
         <f t="shared" si="24"/>
         <v>0.47692885502736343</v>
       </c>
-      <c r="P28" s="9"/>
+      <c r="P28" s="9">
+        <f t="shared" ref="P28" si="25">+P13/P11</f>
+        <v>0.4804803028510588</v>
+      </c>
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
       <c r="S28" s="4"/>
@@ -3475,27 +3580,27 @@
         <v>33</v>
       </c>
       <c r="C29" s="9" t="e">
-        <f t="shared" ref="C29:H29" si="25">+C16/C11</f>
+        <f t="shared" ref="C29:H29" si="26">+C16/C11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D29" s="9" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.10224568387348004</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4.7623852285339566E-2</v>
       </c>
       <c r="G29" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7.5583884317176567E-2</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5.5353516270722214E-2</v>
       </c>
       <c r="I29" s="9">
@@ -3503,30 +3608,33 @@
         <v>0.10267741096958664</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" ref="J29:K29" si="26">+J16/J11</f>
+        <f t="shared" ref="J29:K29" si="27">+J16/J11</f>
         <v>4.7567048134882536E-2</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>2.7793834296724437E-2</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" ref="L29:M29" si="27">+L16/L11</f>
-        <v>-6.7964164349706164E-3</v>
+        <f t="shared" ref="L29:M29" si="28">+L16/L11</f>
+        <v>-5.8248276599155671E-2</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1.5032980518484475E-2</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" ref="N29:O29" si="28">+N16/N11</f>
-        <v>-0.32602283899266365</v>
+        <f t="shared" ref="N29:O29" si="29">+N16/N11</f>
+        <v>-0.24066896353718042</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2.7739027792681583E-2</v>
       </c>
-      <c r="P29" s="9"/>
+      <c r="P29" s="9">
+        <f t="shared" ref="P29" si="30">+P16/P11</f>
+        <v>-3.1408967230569108E-2</v>
+      </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="4"/>
@@ -3581,27 +3689,27 @@
         <v>34</v>
       </c>
       <c r="C30" s="9" t="e">
-        <f t="shared" ref="C30:H30" si="29">+C19/C18</f>
+        <f t="shared" ref="C30:H30" si="31">+C19/C18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D30" s="9" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.25104821802935046</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.17948717948717888</v>
       </c>
       <c r="G30" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.24981074943224771</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.24664879356568309</v>
       </c>
       <c r="I30" s="9">
@@ -3609,30 +3717,33 @@
         <v>0.25118234366789294</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" ref="J30:K30" si="30">+J19/J18</f>
+        <f t="shared" ref="J30:K30" si="32">+J19/J18</f>
         <v>0.31651376146788945</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.26751592356688014</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" ref="L30:M30" si="31">+L19/L18</f>
-        <v>-0.6558171745152358</v>
+        <f t="shared" ref="L30:M30" si="33">+L19/L18</f>
+        <v>-0.61755075311067453</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-2.6319444444444615</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" ref="N30:O30" si="32">+N19/N18</f>
-        <v>4.239073196419179E-2</v>
+        <f t="shared" ref="N30:O30" si="34">+N19/N18</f>
+        <v>4.2261103633916594E-2</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.27146814404432185</v>
       </c>
-      <c r="P30" s="9"/>
+      <c r="P30" s="9">
+        <f t="shared" ref="P30" si="35">+P19/P18</f>
+        <v>8.1743869209809118E-3</v>
+      </c>
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
       <c r="S30" s="4"/>
@@ -18663,5 +18774,6 @@
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{DCA36589-14B8-41CC-BB0C-FA02D922EC0B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>